--- a/12604665.xlsx
+++ b/12604665.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Documents\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EA71FC-CBD2-48BE-94C1-652BE01A8773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1928D4D-0C31-4DF4-B35F-82D0925CCB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,45 @@
   </si>
   <si>
     <t>It was Saturday.</t>
+  </si>
+  <si>
+    <t>Good day, felt a little tired.</t>
+  </si>
+  <si>
+    <t>Busy day, felt tired.</t>
+  </si>
+  <si>
+    <t>Relaxed and enjoyed the day.</t>
+  </si>
+  <si>
+    <t>Had a nice and relaxing day.</t>
+  </si>
+  <si>
+    <t>Slow day, but completed my work.</t>
+  </si>
+  <si>
+    <t>Good and productive day.</t>
+  </si>
+  <si>
+    <t>Good day, stayed on track.</t>
+  </si>
+  <si>
+    <t>Busy day, but completed my work.</t>
+  </si>
+  <si>
+    <t>Relaxed and enjoyed Saturday.</t>
+  </si>
+  <si>
+    <t>Had a peaceful Sunday.</t>
+  </si>
+  <si>
+    <t>Slow day, but did my work.</t>
+  </si>
+  <si>
+    <t>Relaxing Sunday, felt refreshed.</t>
+  </si>
+  <si>
+    <t>Peaceful Sunday, felt refreshed.</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1127,7 @@
         <v>4</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1134,7 +1173,7 @@
         <v>5</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1180,7 +1219,7 @@
         <v>4</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1226,10 +1265,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46251</v>
       </c>
@@ -1272,7 +1311,7 @@
         <v>5</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1318,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1364,7 +1403,7 @@
         <v>5</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1410,10 +1449,10 @@
         <v>4</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46255</v>
       </c>
@@ -1456,7 +1495,7 @@
         <v>5</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1502,7 +1541,7 @@
         <v>5</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1548,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1594,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1686,7 +1725,7 @@
         <v>5</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1807,11 +1846,11 @@
         <v>120</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" ref="I23:I24" si="6">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <f t="shared" ref="I23:I29" si="6">IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
         <v>720</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" ref="J23:J24" si="7">IF(I23="","",1440-I23)</f>
+        <f t="shared" ref="J23:J29" si="7">IF(I23="","",1440-I23)</f>
         <v>720</v>
       </c>
       <c r="K23" s="16">
@@ -1824,7 +1863,7 @@
         <v>4</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1870,496 +1909,1020 @@
         <v>4</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <v>46265</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f>IF(I25="","",1440-I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>120</v>
+      </c>
+      <c r="E25" s="14">
+        <v>45</v>
+      </c>
+      <c r="F25" s="14">
+        <v>300</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="6"/>
+        <v>885</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="7"/>
+        <v>555</v>
+      </c>
+      <c r="K25" s="16">
+        <v>5</v>
+      </c>
+      <c r="L25" s="16">
+        <v>5</v>
+      </c>
+      <c r="M25" s="16">
+        <v>5</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>46266</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f>IF(I26="","",1440-I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="B26" s="14">
+        <v>360</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>300</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="6"/>
+        <v>915</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="7"/>
+        <v>525</v>
+      </c>
+      <c r="K26" s="16">
+        <v>4</v>
+      </c>
+      <c r="L26" s="16">
+        <v>5</v>
+      </c>
+      <c r="M26" s="16">
+        <v>4</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" ref="I27:I34" si="8">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" ref="J27:J34" si="9">IF(I27="","",1440-I27)</f>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+      <c r="A27" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>40</v>
+      </c>
+      <c r="D27" s="14">
+        <v>120</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>240</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4</v>
+      </c>
+      <c r="H27" s="14">
+        <v>90</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="6"/>
+        <v>880</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="7"/>
+        <v>560</v>
+      </c>
+      <c r="K27" s="16">
+        <v>4</v>
+      </c>
+      <c r="L27" s="16">
+        <v>4</v>
+      </c>
+      <c r="M27" s="16">
+        <v>5</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>90</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>240</v>
+      </c>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>90</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="6"/>
+        <v>900</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="7"/>
+        <v>540</v>
+      </c>
+      <c r="K28" s="16">
+        <v>4</v>
+      </c>
+      <c r="L28" s="16">
+        <v>4</v>
+      </c>
+      <c r="M28" s="16">
+        <v>5</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>60</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>360</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>40</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="6"/>
+        <v>820</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="7"/>
+        <v>620</v>
+      </c>
+      <c r="K29" s="16">
+        <v>5</v>
+      </c>
+      <c r="L29" s="16">
+        <v>5</v>
+      </c>
+      <c r="M29" s="16">
+        <v>5</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>90</v>
+      </c>
+      <c r="E30" s="14">
+        <v>60</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" ref="I30:I45" si="8">IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <v>720</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" ref="J30:J45" si="9">IF(I30="","",1440-I30)</f>
+        <v>720</v>
+      </c>
+      <c r="K30" s="16">
+        <v>3</v>
+      </c>
+      <c r="L30" s="16">
+        <v>5</v>
+      </c>
+      <c r="M30" s="16">
+        <v>4</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B31" s="14">
+        <v>480</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>90</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="K31" s="16">
+        <v>5</v>
+      </c>
+      <c r="L31" s="16">
+        <v>5</v>
+      </c>
+      <c r="M31" s="16">
+        <v>4</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>120</v>
+      </c>
+      <c r="E32" s="14">
+        <v>45</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>60</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>885</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>555</v>
+      </c>
+      <c r="K32" s="16">
+        <v>5</v>
+      </c>
+      <c r="L32" s="16">
+        <v>5</v>
+      </c>
+      <c r="M32" s="16">
+        <v>5</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B33" s="14">
+        <v>360</v>
+      </c>
+      <c r="C33" s="14">
+        <v>45</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>300</v>
+      </c>
+      <c r="G33" s="14">
+        <v>5</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>525</v>
+      </c>
+      <c r="K33" s="16">
+        <v>4</v>
+      </c>
+      <c r="L33" s="16">
+        <v>5</v>
+      </c>
+      <c r="M33" s="16">
+        <v>4</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B34" s="14">
+        <v>360</v>
+      </c>
+      <c r="C34" s="14">
+        <v>40</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>30</v>
+      </c>
+      <c r="F34" s="14">
+        <v>240</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>90</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>560</v>
+      </c>
+      <c r="K34" s="16">
+        <v>4</v>
+      </c>
+      <c r="L34" s="16">
+        <v>4</v>
+      </c>
+      <c r="M34" s="16">
+        <v>5</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>30</v>
+      </c>
+      <c r="F35" s="14">
+        <v>240</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>90</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="K35" s="16">
+        <v>4</v>
+      </c>
+      <c r="L35" s="16">
+        <v>4</v>
+      </c>
+      <c r="M35" s="16">
+        <v>5</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>60</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>360</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>40</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K36" s="16">
+        <v>5</v>
+      </c>
+      <c r="L36" s="16">
+        <v>5</v>
+      </c>
+      <c r="M36" s="16">
+        <v>5</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>30</v>
+      </c>
+      <c r="D37" s="14">
+        <v>90</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>120</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K37" s="16">
+        <v>3</v>
+      </c>
+      <c r="L37" s="16">
+        <v>5</v>
+      </c>
+      <c r="M37" s="16">
+        <v>4</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="A38" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B38" s="14">
+        <v>480</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>90</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>120</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="8"/>
+        <v>780</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="9"/>
+        <v>660</v>
+      </c>
+      <c r="K38" s="16">
+        <v>5</v>
+      </c>
+      <c r="L38" s="16">
+        <v>5</v>
+      </c>
+      <c r="M38" s="16">
+        <v>4</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+      <c r="A39" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B39" s="14">
+        <v>360</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>120</v>
+      </c>
+      <c r="E39" s="14">
+        <v>45</v>
+      </c>
+      <c r="F39" s="14">
+        <v>300</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>60</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="8"/>
+        <v>885</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="9"/>
+        <v>555</v>
+      </c>
+      <c r="K39" s="16">
+        <v>5</v>
+      </c>
+      <c r="L39" s="16">
+        <v>5</v>
+      </c>
+      <c r="M39" s="16">
+        <v>5</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+      <c r="A40" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B40" s="14">
+        <v>360</v>
+      </c>
+      <c r="C40" s="14">
+        <v>45</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>5</v>
+      </c>
+      <c r="H40" s="14">
+        <v>60</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="8"/>
+        <v>915</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="9"/>
+        <v>525</v>
+      </c>
+      <c r="K40" s="16">
+        <v>4</v>
+      </c>
+      <c r="L40" s="16">
+        <v>5</v>
+      </c>
+      <c r="M40" s="16">
+        <v>4</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+      <c r="A41" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B41" s="14">
+        <v>360</v>
+      </c>
+      <c r="C41" s="14">
+        <v>40</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>30</v>
+      </c>
+      <c r="F41" s="14">
+        <v>240</v>
+      </c>
+      <c r="G41" s="14">
+        <v>4</v>
+      </c>
+      <c r="H41" s="14">
+        <v>90</v>
+      </c>
+      <c r="I41" s="15">
+        <f t="shared" si="8"/>
+        <v>880</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" si="9"/>
+        <v>560</v>
+      </c>
+      <c r="K41" s="16">
+        <v>4</v>
+      </c>
+      <c r="L41" s="16">
+        <v>4</v>
+      </c>
+      <c r="M41" s="16">
+        <v>5</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+      <c r="A42" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B42" s="14">
+        <v>420</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>90</v>
+      </c>
+      <c r="E42" s="14">
+        <v>30</v>
+      </c>
+      <c r="F42" s="14">
+        <v>240</v>
+      </c>
+      <c r="G42" s="14">
+        <v>4</v>
+      </c>
+      <c r="H42" s="14">
+        <v>90</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="8"/>
+        <v>900</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="9"/>
+        <v>540</v>
+      </c>
+      <c r="K42" s="16">
+        <v>4</v>
+      </c>
+      <c r="L42" s="16">
+        <v>4</v>
+      </c>
+      <c r="M42" s="16">
+        <v>5</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+      <c r="A43" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B43" s="14">
+        <v>360</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>60</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>360</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>40</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="8"/>
+        <v>820</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="9"/>
+        <v>620</v>
+      </c>
+      <c r="K43" s="16">
+        <v>5</v>
+      </c>
+      <c r="L43" s="16">
+        <v>5</v>
+      </c>
+      <c r="M43" s="16">
+        <v>5</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+      <c r="A44" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>30</v>
+      </c>
+      <c r="D44" s="14">
+        <v>90</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>120</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="8"/>
+        <v>720</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="9"/>
+        <v>720</v>
+      </c>
+      <c r="K44" s="16">
+        <v>3</v>
+      </c>
+      <c r="L44" s="16">
+        <v>5</v>
+      </c>
+      <c r="M44" s="16">
+        <v>4</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+      <c r="A45" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>90</v>
+      </c>
+      <c r="E45" s="14">
+        <v>60</v>
+      </c>
+      <c r="F45" s="14">
+        <v>0</v>
+      </c>
+      <c r="G45" s="14">
+        <v>0</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="8"/>
+        <v>780</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="9"/>
+        <v>660</v>
+      </c>
+      <c r="K45" s="16">
+        <v>5</v>
+      </c>
+      <c r="L45" s="16">
+        <v>5</v>
+      </c>
+      <c r="M45" s="16">
+        <v>4</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+      <c r="A46" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B46" s="14">
+        <v>360</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>45</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>60</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" ref="I46" si="10">IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
+        <v>885</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" ref="J46" si="11">IF(I46="","",1440-I46)</f>
+        <v>555</v>
+      </c>
+      <c r="K46" s="16">
+        <v>5</v>
+      </c>
+      <c r="L46" s="16">
+        <v>5</v>
+      </c>
+      <c r="M46" s="16">
+        <v>5</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
@@ -2877,11 +3440,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="10">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="12">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="11">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="13">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2899,11 +3462,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2921,11 +3484,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2943,11 +3506,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2965,11 +3528,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2987,11 +3550,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3009,11 +3572,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3031,11 +3594,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3053,11 +3616,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3075,11 +3638,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3097,11 +3660,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3119,11 +3682,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3141,11 +3704,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3163,11 +3726,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3185,11 +3748,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3207,11 +3770,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3229,11 +3792,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3251,11 +3814,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3273,11 +3836,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3295,11 +3858,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3317,11 +3880,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3339,11 +3902,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3361,11 +3924,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3383,11 +3946,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3405,11 +3968,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3427,11 +3990,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3449,11 +4012,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3471,11 +4034,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3493,11 +4056,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3515,11 +4078,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3537,11 +4100,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3559,11 +4122,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3581,11 +4144,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3603,11 +4166,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3625,11 +4188,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3647,11 +4210,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3669,11 +4232,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3691,11 +4254,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3713,11 +4276,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3735,11 +4298,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3757,11 +4320,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3779,11 +4342,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3801,11 +4364,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3823,11 +4386,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3845,11 +4408,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3867,11 +4430,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3889,11 +4452,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3911,11 +4474,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3933,11 +4496,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3955,11 +4518,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3977,11 +4540,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3999,11 +4562,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4021,11 +4584,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4043,11 +4606,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4065,11 +4628,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4087,11 +4650,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4109,11 +4672,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4131,11 +4694,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4153,11 +4716,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4175,11 +4738,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4197,11 +4760,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4219,11 +4782,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4241,11 +4804,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4263,11 +4826,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4285,11 +4848,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="12">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="14">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="13">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="15">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4307,11 +4870,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4329,11 +4892,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4351,11 +4914,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4373,11 +4936,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4395,11 +4958,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4417,11 +4980,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4439,11 +5002,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4461,11 +5024,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4483,11 +5046,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4505,11 +5068,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4527,11 +5090,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4549,11 +5112,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4571,11 +5134,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4593,11 +5156,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4615,11 +5178,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4637,11 +5200,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4659,11 +5222,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4681,11 +5244,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4703,11 +5266,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4725,11 +5288,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4747,11 +5310,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4769,11 +5332,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4791,11 +5354,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4813,11 +5376,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4835,11 +5398,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4857,11 +5420,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4879,11 +5442,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4901,11 +5464,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4923,11 +5486,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4945,11 +5508,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4967,11 +5530,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4989,11 +5552,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5011,11 +5574,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5033,11 +5596,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5055,11 +5618,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5077,11 +5640,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5099,11 +5662,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5121,11 +5684,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5143,11 +5706,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5165,11 +5728,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5187,11 +5750,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5209,11 +5772,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5231,11 +5794,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5253,11 +5816,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5275,11 +5838,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5297,11 +5860,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5319,11 +5882,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5341,11 +5904,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5363,11 +5926,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5385,11 +5948,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5407,11 +5970,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5429,11 +5992,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5451,11 +6014,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5473,11 +6036,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5495,11 +6058,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5517,11 +6080,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5539,11 +6102,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5561,11 +6124,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5583,11 +6146,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5605,11 +6168,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5627,11 +6190,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5649,11 +6212,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5671,11 +6234,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5693,11 +6256,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="14">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="16">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="15">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="17">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5715,11 +6278,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5737,11 +6300,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5759,11 +6322,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5781,11 +6344,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5803,11 +6366,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5825,11 +6388,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5847,11 +6410,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5869,11 +6432,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5891,11 +6454,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5913,11 +6476,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5935,11 +6498,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5957,11 +6520,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5979,11 +6542,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6001,11 +6564,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6023,11 +6586,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6045,11 +6608,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6067,11 +6630,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6089,11 +6652,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6111,11 +6674,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6133,11 +6696,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6155,11 +6718,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6177,11 +6740,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6199,11 +6762,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6221,11 +6784,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6243,11 +6806,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6265,11 +6828,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6287,11 +6850,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6309,11 +6872,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6331,11 +6894,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6353,11 +6916,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6375,11 +6938,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6397,11 +6960,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6419,11 +6982,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6441,11 +7004,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6463,11 +7026,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6485,11 +7048,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6507,11 +7070,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6529,11 +7092,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6551,11 +7114,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6573,11 +7136,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6595,11 +7158,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6617,11 +7180,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6639,11 +7202,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6661,11 +7224,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6683,11 +7246,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6705,11 +7268,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6727,11 +7290,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6749,11 +7312,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6771,11 +7334,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6793,11 +7356,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6815,11 +7378,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6837,11 +7400,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6859,11 +7422,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6881,11 +7444,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6903,11 +7466,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6925,11 +7488,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6947,11 +7510,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6969,11 +7532,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6991,11 +7554,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7013,11 +7576,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7035,11 +7598,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7057,11 +7620,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7079,11 +7642,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7101,11 +7664,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="16">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="18">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="17">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="19">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7123,11 +7686,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7145,11 +7708,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7167,11 +7730,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7189,11 +7752,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7211,11 +7774,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7233,11 +7796,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7255,11 +7818,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7277,11 +7840,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7299,11 +7862,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7321,11 +7884,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7343,11 +7906,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7365,11 +7928,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7387,11 +7950,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7409,11 +7972,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7431,11 +7994,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7453,11 +8016,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7475,11 +8038,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7497,11 +8060,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7519,11 +8082,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7541,11 +8104,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7563,11 +8126,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7585,11 +8148,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7607,11 +8170,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7629,11 +8192,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7651,11 +8214,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7673,11 +8236,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7695,11 +8258,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7717,11 +8280,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7739,11 +8302,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7761,11 +8324,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7783,11 +8346,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7805,11 +8368,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7827,11 +8390,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7849,11 +8412,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7871,11 +8434,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7893,11 +8456,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7915,11 +8478,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7937,11 +8500,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7959,11 +8522,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7981,11 +8544,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8003,11 +8566,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8025,11 +8588,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8047,11 +8610,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8069,11 +8632,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8091,11 +8654,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8113,11 +8676,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8135,11 +8698,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8157,11 +8720,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8179,11 +8742,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8201,11 +8764,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8223,11 +8786,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8245,11 +8808,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8267,11 +8830,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8289,11 +8852,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8311,11 +8874,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8333,11 +8896,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8355,11 +8918,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8377,11 +8940,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8399,11 +8962,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8421,11 +8984,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8443,11 +9006,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8465,11 +9028,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8487,11 +9050,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8509,11 +9072,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="18">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="20">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="19">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="21">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8531,11 +9094,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8553,11 +9116,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8575,11 +9138,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8597,11 +9160,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8619,11 +9182,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8641,11 +9204,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8663,11 +9226,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8685,11 +9248,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8707,11 +9270,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8729,11 +9292,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8751,11 +9314,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8773,11 +9336,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8795,11 +9358,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8817,11 +9380,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8839,11 +9402,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8861,11 +9424,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8883,11 +9446,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8905,11 +9468,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8927,11 +9490,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8949,11 +9512,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8971,11 +9534,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8993,11 +9556,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9015,11 +9578,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9037,11 +9600,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9059,11 +9622,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9081,11 +9644,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9103,11 +9666,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9125,11 +9688,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9147,11 +9710,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9169,11 +9732,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9191,11 +9754,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9213,11 +9776,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9235,11 +9798,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9257,11 +9820,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9279,11 +9842,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9301,11 +9864,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9323,11 +9886,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9345,11 +9908,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9367,11 +9930,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9389,11 +9952,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9411,11 +9974,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9433,11 +9996,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9455,11 +10018,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9477,11 +10040,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9499,11 +10062,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9521,11 +10084,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9543,11 +10106,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9565,11 +10128,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9587,11 +10150,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9609,11 +10172,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9631,11 +10194,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9653,11 +10216,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9675,11 +10238,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9697,11 +10260,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9719,11 +10282,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9741,11 +10304,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9763,11 +10326,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9785,11 +10348,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9807,11 +10370,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9829,11 +10392,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9851,11 +10414,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9873,11 +10436,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9895,11 +10458,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9917,11 +10480,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="20">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="22">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="21">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="23">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9939,11 +10502,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9961,11 +10524,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9983,11 +10546,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10005,11 +10568,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10027,11 +10590,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -10049,11 +10612,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -10071,11 +10634,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -10093,11 +10656,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -10115,11 +10678,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -10137,11 +10700,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -10159,11 +10722,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K401" s="16"/>
